--- a/manuscript/submission_data/source_data/Source_Data_Figure_2.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Figure_2.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Panel_E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_E" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -910,10 +910,26 @@
           <t>1083167</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>public_longread_or_hybrid_assembly</t>
@@ -941,17 +957,17 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1082127</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>1083167</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>example_assembly</t>
+          <t>read_reference</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -1102,7 +1118,11 @@
           <t>1099808</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>public_longread_or_hybrid_assembly</t>
@@ -1277,9 +1297,21 @@
           <t>Illumina MiSeq; PacBio</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>NC_002929.2</t>
@@ -1422,8 +1454,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>insertion_like</t>
@@ -1489,16 +1529,36 @@
           <t>79033</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>assembly_only</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AB16" t="inlineStr">
         <is>
           <t>Reference-coordinate fields are populated only when read-level or example-assembly coordinates are present in the current ledgers; blank fields should not be interpreted as absence of a junction.</t>
@@ -1516,17 +1576,17 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>77989</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>79033</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>example_assembly</t>
+          <t>read_reference</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -1543,7 +1603,11 @@
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>assembly_only</t>
@@ -1591,8 +1655,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>insertion_like</t>
@@ -1658,16 +1730,36 @@
           <t>310</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>assembly_only</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AB17" t="inlineStr">
         <is>
           <t>Reference-coordinate fields are populated only when read-level or example-assembly coordinates are present in the current ledgers; blank fields should not be interpreted as absence of a junction.</t>
@@ -1685,17 +1777,17 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>example_assembly</t>
+          <t>read_reference</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1712,7 +1804,11 @@
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>assembly_only</t>
@@ -2238,9 +2334,21 @@
           <t>PacBio RSII; Illumina HiSeq</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
           <t>NC_002929.2</t>
@@ -2450,16 +2558,36 @@
           <t>1417126</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
           <t>read_validation_unresolved</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AB21" t="inlineStr">
         <is>
           <t>Reference-coordinate fields are populated only when read-level or example-assembly coordinates are present in the current ledgers; blank fields should not be interpreted as absence of a junction.</t>
@@ -2477,17 +2605,17 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1416083</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>1417126</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>example_assembly</t>
+          <t>read_reference</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2520,7 +2648,11 @@
           <t>not_run</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -2635,16 +2767,36 @@
           <t>1417171</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr">
         <is>
           <t>read_validation_unresolved</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AB22" t="inlineStr">
         <is>
           <t>Reference-coordinate fields are populated only when read-level or example-assembly coordinates are present in the current ledgers; blank fields should not be interpreted as absence of a junction.</t>
@@ -2662,17 +2814,17 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1416127</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>1417171</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>example_assembly</t>
+          <t>read_reference</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2705,7 +2857,11 @@
           <t>not_run</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -2745,8 +2901,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>insertion_like</t>
@@ -2812,16 +2976,36 @@
           <t>17931</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr">
         <is>
           <t>assembly_only</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AB23" t="inlineStr">
         <is>
           <t>Reference-coordinate fields are populated only when read-level or example-assembly coordinates are present in the current ledgers; blank fields should not be interpreted as absence of a junction.</t>
@@ -2839,17 +3023,17 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>example_assembly</t>
+          <t>read_reference</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -2866,7 +3050,11 @@
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>assembly_only</t>
@@ -2934,9 +3122,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>rule_medium</t>
@@ -2962,9 +3162,21 @@
           <t>PacBio RSII; Illumina HiSeq</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>NC_002929.2</t>
@@ -3025,7 +3237,11 @@
           <t>read_reference</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AI24" t="inlineStr">
         <is>
           <t>target_site_duplication_recovered</t>
@@ -3123,9 +3339,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>rule_medium</t>
@@ -3226,7 +3454,11 @@
           <t>read_reference</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AI25" t="inlineStr">
         <is>
           <t>target_site_duplication_recovered</t>
@@ -3324,9 +3556,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>rule_medium</t>
@@ -3352,13 +3596,41 @@
           <t>PacBio RSII; Illumina MiSeq</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr">
         <is>
           <t>public_longread_or_hybrid_assembly</t>
@@ -3384,14 +3656,26 @@
           <t>public_longread_or_hybrid_assembly</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>example_assembly</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr"/>
+          <t>read_reference</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AI26" t="inlineStr">
         <is>
           <t>not_recovered_current_public_data</t>
@@ -4303,7 +4587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W58"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4521,12 +4805,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5285,12 +5569,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5699,12 +5983,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5749,7 +6033,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.6179775280898876</t>
+          <t>0.6170212765957447</t>
         </is>
       </c>
     </row>
@@ -5771,12 +6055,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5821,7 +6105,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.19850187265917604</t>
+          <t>0.20309477756286268</t>
         </is>
       </c>
     </row>
@@ -5843,12 +6127,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5893,7 +6177,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.11423220973782772</t>
+          <t>0.11218568665377177</t>
         </is>
       </c>
     </row>
@@ -5905,22 +6189,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5937,7 +6221,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.031835205992509365</t>
+          <t>0.027079303675048357</t>
         </is>
       </c>
     </row>
@@ -5964,7 +6248,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6009,7 +6293,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.013108614232209739</t>
+          <t>0.013539651837524178</t>
         </is>
       </c>
     </row>
@@ -6031,12 +6315,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6081,7 +6365,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.013108614232209739</t>
+          <t>0.01160541586073501</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6392,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6153,7 +6437,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.00749063670411985</t>
+          <t>0.007736943907156673</t>
         </is>
       </c>
     </row>
@@ -6165,22 +6449,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
+          <t>prn_evt_insufficient__partial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>insufficient_data</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6188,44 +6472,16 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.0018726591760299626</t>
+          <t>0.0038684719535783366</t>
         </is>
       </c>
     </row>
@@ -6237,415 +6493,354 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>prn_evt_rearrangement__within_contig__cov94</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>coding_disrupted_other</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0.0019342359767891683</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov66</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>coding_disrupted_inversion_or_rearrangement</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>public_longread_or_hybrid_assembly</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0.0018726591760299626</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0.0019342359767891683</t>
+        </is>
+      </c>
+    </row>
     <row r="40"/>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>manuscript/figure_data/prn_junction_confidence_matrix.tsv</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>found</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>prn_event_id</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>event_label</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>mechanism_call</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>event_subcategory</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>sample_count</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>country_count</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>year_min</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>year_max</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
+      <c r="I45" s="1" t="inlineStr">
         <is>
           <t>insertion_subject_gap_bp</t>
         </is>
       </c>
-      <c r="J44" s="1" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>orientation</t>
         </is>
       </c>
-      <c r="K44" s="1" t="inlineStr">
+      <c r="K45" s="1" t="inlineStr">
         <is>
           <t>breakpoint_coordinate_basis</t>
         </is>
       </c>
-      <c r="L44" s="1" t="inlineStr">
+      <c r="L45" s="1" t="inlineStr">
         <is>
           <t>breakpoint_left</t>
         </is>
       </c>
-      <c r="M44" s="1" t="inlineStr">
+      <c r="M45" s="1" t="inlineStr">
         <is>
           <t>breakpoint_right</t>
         </is>
       </c>
-      <c r="N44" s="1" t="inlineStr">
+      <c r="N45" s="1" t="inlineStr">
         <is>
           <t>representative_tsd_direct_repeats</t>
         </is>
       </c>
-      <c r="O44" s="1" t="inlineStr">
+      <c r="O45" s="1" t="inlineStr">
         <is>
           <t>tsd_or_flank_sequence_status</t>
         </is>
       </c>
-      <c r="P44" s="1" t="inlineStr">
+      <c r="P45" s="1" t="inlineStr">
         <is>
           <t>supporting_read_count</t>
         </is>
       </c>
-      <c r="Q44" s="1" t="inlineStr">
+      <c r="Q45" s="1" t="inlineStr">
         <is>
           <t>supporting_validation_rows</t>
         </is>
       </c>
-      <c r="R44" s="1" t="inlineStr">
+      <c r="R45" s="1" t="inlineStr">
         <is>
           <t>tsd_supported_validation_rows</t>
         </is>
       </c>
-      <c r="S44" s="1" t="inlineStr">
+      <c r="S45" s="1" t="inlineStr">
         <is>
           <t>max_total_clipped_reads</t>
         </is>
       </c>
-      <c r="T44" s="1" t="inlineStr">
+      <c r="T45" s="1" t="inlineStr">
         <is>
           <t>validation_level</t>
         </is>
       </c>
-      <c r="U44" s="1" t="inlineStr">
+      <c r="U45" s="1" t="inlineStr">
         <is>
           <t>confidence_tier</t>
         </is>
       </c>
-      <c r="V44" s="1" t="inlineStr">
+      <c r="V45" s="1" t="inlineStr">
         <is>
           <t>priority_origin_ids</t>
         </is>
       </c>
-      <c r="W44" s="1" t="inlineStr">
+      <c r="W45" s="1" t="inlineStr">
         <is>
           <t>junction_interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>is481:is481:gap1043</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>coding_disrupted_is481</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>IS481 insertion</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>read_reference</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>1099682</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>1099688</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>ACTAGG</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>target_site_duplication_recovered</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>tier_1_read_backed_tsd_recovered</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>origin_0001;origin_0002;origin_0003;origin_0005;origin_0006;origin_0007;origin_0008;origin_0009;origin_0010</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>representative junction and TSD support; not every assembly resolves a finished junction</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>prn_evt_rearrangement__within_contig__cov58</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>rearrangement:within_contig:cov58</t>
+          <t>is481:is481:gap1043</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>coding_disrupted_inversion_or_rearrangement</t>
+          <t>coding_disrupted_is481</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Inversion / rearrangement</t>
+          <t>IS481 insertion</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>370</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>read_reference</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1099682</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1099688</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ACTAGG</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>read_reference</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>1099682</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>1099688</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>ACTAGG</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>target_site_duplication_recovered</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr">
         <is>
           <t>read_backed_supported</t>
@@ -6658,7 +6853,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>origin_0002;origin_0004;origin_0008</t>
+          <t>origin_0001;origin_0002;origin_0003;origin_0005;origin_0006;origin_0007;origin_0008;origin_0009;origin_0010</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6670,12 +6865,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>prn_evt_rearrangement__within_contig__cov91</t>
+          <t>prn_evt_rearrangement__within_contig__cov58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>rearrangement:within_contig:cov91</t>
+          <t>rearrangement:within_contig:cov58</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6690,22 +6885,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6721,17 +6916,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1098329</t>
+          <t>1099682</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1098335</t>
+          <t>1099688</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GCTAGA</t>
+          <t>ACTAGG</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -6741,12 +6936,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -6763,7 +6958,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>origin_0005</t>
+          <t>origin_0002;origin_0004;origin_0008</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6775,54 +6970,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1042</t>
+          <t>prn_evt_rearrangement__within_contig__cov91</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>other_disruption:insertion_like:gap1042</t>
+          <t>rearrangement:within_contig:cov91</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Other disruptions</t>
+          <t>Inversion / rearrangement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1042</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>read_reference</t>
@@ -6830,17 +7021,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1099682</t>
+          <t>1098329</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1099688</t>
+          <t>1098335</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>ACTAGG</t>
+          <t>GCTAGA</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -6850,24 +7041,16 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
           <t>read_backed_supported</t>
@@ -6878,7 +7061,11 @@
           <t>tier_1_read_backed_tsd_recovered</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>origin_0005</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>representative junction and TSD support; not every assembly resolves a finished junction</t>
@@ -6888,128 +7075,140 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1042</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1042</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>is481:is481:gap1042</t>
+          <t>other_disruption:insertion_like:gap1042</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>coding_disrupted_is481</t>
+          <t>coding_disrupted_other</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IS481 insertion</t>
+          <t>Other disruptions</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>read_reference</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1099682</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1099688</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ACTAGG</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1042</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>read_reference</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>1099688</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>1099808</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>read_interval_without_tsd</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>public_longread_or_hybrid_assembly</t>
+          <t>read_backed_supported</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>tier_2_public_longread_or_hybrid</t>
+          <t>tier_1_read_backed_tsd_recovered</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
-          <t>event-class support without universal read-resolved junctions</t>
+          <t>representative junction and TSD support; not every assembly resolves a finished junction</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1041</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1042</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>other_disruption:insertion_like:gap1041</t>
+          <t>is481:is481:gap1042</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>coding_disrupted_is481</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Other disruptions</t>
+          <t>IS481 insertion</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7029,7 +7228,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7044,85 +7243,73 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1096735</t>
+          <t>1099688</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1097761</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>ACTAGG</t>
-        </is>
-      </c>
+          <t>1099808</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>target_site_duplication_recovered</t>
+          <t>read_interval_without_tsd</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>read_backed_supported</t>
+          <t>public_longread_or_hybrid_assembly</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>tier_1_read_backed_tsd_recovered</t>
+          <t>tier_2_public_longread_or_hybrid</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
-          <t>representative junction and TSD support; not every assembly resolves a finished junction</t>
+          <t>event-class support without universal read-resolved junctions</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1041</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1041</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>is481:is481:gap1041</t>
+          <t>other_disruption:insertion_like:gap1041</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>coding_disrupted_is481</t>
+          <t>coding_disrupted_other</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IS481 insertion</t>
+          <t>Other disruptions</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7132,12 +7319,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7147,70 +7334,90 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>example_assembly</t>
+          <t>read_reference</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1082127</t>
+          <t>1096735</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1083167</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>1097761</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ACTAGG</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>assembly_coordinate_only</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>public_longread_or_hybrid_assembly</t>
+          <t>read_backed_supported</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>tier_2_public_longread_or_hybrid</t>
+          <t>tier_1_read_backed_tsd_recovered</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
-          <t>event-class support without universal read-resolved junctions</t>
+          <t>representative junction and TSD support; not every assembly resolves a finished junction</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1041</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>other_disruption:insertion_like:gap1040</t>
+          <t>is481:is481:gap1041</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>coding_disrupted_is481</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Other disruptions</t>
+          <t>IS481 insertion</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7220,189 +7427,193 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>read_reference</t>
+          <t>example_assembly</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1099683</t>
+          <t>1082127</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1099688</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>ACTAGG</t>
-        </is>
-      </c>
+          <t>1083167</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>target_site_duplication_recovered</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>assembly_coordinate_only</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>read_backed_supported</t>
+          <t>public_longread_or_hybrid_assembly</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>tier_1_read_backed_tsd_recovered</t>
+          <t>tier_2_public_longread_or_hybrid</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
-          <t>representative junction and TSD support; not every assembly resolves a finished junction</t>
+          <t>event-class support without universal read-resolved junctions</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1045</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>is481:is481:gap1045</t>
+          <t>other_disruption:insertion_like:gap1040</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>coding_disrupted_is481</t>
+          <t>coding_disrupted_other</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>IS481 insertion</t>
+          <t>Other disruptions</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>read_reference</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1099683</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1099688</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ACTAGG</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>example_assembly</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>77989</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>79033</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>assembly_coordinate_only</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>assembly_only</t>
+          <t>read_backed_supported</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>tier_3_assembly_or_rule_supported</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>origin_0005</t>
-        </is>
-      </c>
+          <t>tier_1_read_backed_tsd_recovered</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
-          <t>event-class support without universal read-resolved junctions</t>
+          <t>representative junction and TSD support; not every assembly resolves a finished junction</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap54</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1045</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>is481:is481:gap54</t>
+          <t>is481:is481:gap1045</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7429,7 +7640,7 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7444,12 +7655,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>77989</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>79033</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7486,22 +7697,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1044</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>other_disruption:insertion_like:gap1044</t>
+          <t>is481:is481:gap54</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>coding_disrupted_is481</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Other disruptions</t>
+          <t>IS481 insertion</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7511,22 +7722,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7541,12 +7744,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1416083</t>
+          <t>257</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1417126</t>
+          <t>310</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7555,29 +7758,25 @@
           <t>assembly_coordinate_only</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t>read_validation_unresolved</t>
+          <t>assembly_only</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>tier_4_validation_unresolved</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr"/>
+          <t>tier_3_assembly_or_rule_supported</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>origin_0005</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>event-class support without universal read-resolved junctions</t>
@@ -7587,12 +7786,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1045</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1044</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>other_disruption:insertion_like:gap1045</t>
+          <t>other_disruption:insertion_like:gap1044</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7627,7 +7826,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7642,12 +7841,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1416127</t>
+          <t>1416083</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1417171</t>
+          <t>1417126</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7688,12 +7887,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap204</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1045</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>other_disruption:insertion_like:gap204</t>
+          <t>other_disruption:insertion_like:gap1045</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7713,14 +7912,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7735,12 +7942,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>1416127</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>1417171</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7749,25 +7956,29 @@
           <t>assembly_coordinate_only</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t>assembly_only</t>
+          <t>read_validation_unresolved</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>tier_3_assembly_or_rule_supported</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>origin_0005</t>
-        </is>
-      </c>
+          <t>tier_4_validation_unresolved</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>event-class support without universal read-resolved junctions</t>
@@ -7777,22 +7988,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>prn_evt_rearrangement__within_contig__cov94</t>
+          <t>prn_evt_other_disruption__insertion_like__gap204</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>rearrangement:within_contig:cov94</t>
+          <t>other_disruption:insertion_like:gap204</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>coding_disrupted_inversion_or_rearrangement</t>
+          <t>coding_disrupted_other</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Inversion / rearrangement</t>
+          <t>Other disruptions</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7802,36 +8013,40 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>example_assembly</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>17728</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>17931</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>not_recovered_current_public_data</t>
+          <t>assembly_coordinate_only</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -7840,16 +8055,101 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
+          <t>assembly_only</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>tier_3_assembly_or_rule_supported</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>origin_0005</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>event-class support without universal read-resolved junctions</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov94</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>rearrangement:within_contig:cov94</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Inversion / rearrangement</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>example_assembly</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>not_recovered_current_public_data</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
           <t>public_longread_or_hybrid_assembly</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>tier_2_public_longread_or_hybrid</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr">
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
         <is>
           <t>event-class support without universal read-resolved junctions</t>
         </is>
@@ -7866,7 +8166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -8075,12 +8375,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -8839,12 +9139,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -9253,12 +9553,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9303,7 +9603,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.6179775280898876</t>
+          <t>0.6170212765957447</t>
         </is>
       </c>
     </row>
@@ -9325,12 +9625,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9375,7 +9675,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.19850187265917604</t>
+          <t>0.20309477756286268</t>
         </is>
       </c>
     </row>
@@ -9397,12 +9697,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9447,7 +9747,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.11423220973782772</t>
+          <t>0.11218568665377177</t>
         </is>
       </c>
     </row>
@@ -9459,22 +9759,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9491,7 +9791,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.031835205992509365</t>
+          <t>0.027079303675048357</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9818,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9563,7 +9863,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.013108614232209739</t>
+          <t>0.013539651837524178</t>
         </is>
       </c>
     </row>
@@ -9585,12 +9885,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9635,7 +9935,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.013108614232209739</t>
+          <t>0.01160541586073501</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9707,7 +10007,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.00749063670411985</t>
+          <t>0.007736943907156673</t>
         </is>
       </c>
     </row>
@@ -9719,22 +10019,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
+          <t>prn_evt_insufficient__partial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>insufficient_data</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9742,44 +10042,16 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.0018726591760299626</t>
+          <t>0.0038684719535783366</t>
         </is>
       </c>
     </row>
@@ -9791,67 +10063,111 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>prn_evt_rearrangement__within_contig__cov94</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>coding_disrupted_other</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0.0019342359767891683</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov66</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>coding_disrupted_inversion_or_rearrangement</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>public_longread_or_hybrid_assembly</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0.0018726591760299626</t>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0.0019342359767891683</t>
         </is>
       </c>
     </row>
@@ -10194,12 +10510,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -10214,37 +10530,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.5996758508914101</t>
+          <t>0.6412478336221837</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.8816855753646677</t>
+          <t>0.9428076256499134</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.9627228525121555</t>
+          <t>0.9722703639514731</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.4066180005201097</t>
+          <t>0.46014315364537195</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.29192339164165</t>
+          <t>1.1247880603691582</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3.63978055098988</t>
+          <t>3.079564098070489</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.8097244732576986</t>
+          <t>0.8248328794256005</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -10259,7 +10575,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.08515559157212318</t>
+          <t>0.09103708838821492</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -10269,7 +10585,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0.24147649918962724</t>
+          <t>0.2575310225303293</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -10279,7 +10595,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>14.832717215541487</t>
+          <t>13.842638296012616</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -10289,7 +10605,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.08139703943814154</t>
+          <t>0.08159509779648427</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -10308,7 +10624,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
+          <t>structurally_resolved_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10641,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10345,37 +10661,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.5996758508914101</t>
+          <t>0.6412478336221837</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.8816855753646677</t>
+          <t>0.9428076256499134</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.9627228525121555</t>
+          <t>0.9722703639514731</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.4066180005201097</t>
+          <t>0.46014315364537195</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.29192339164165</t>
+          <t>1.1247880603691582</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3.63978055098988</t>
+          <t>3.079564098070489</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.8097244732576986</t>
+          <t>0.8248328794256005</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -10390,7 +10706,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.19212350081037277</t>
+          <t>0.19634350086655114</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -10400,7 +10716,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.42306126418152346</t>
+          <t>0.43198197573656855</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -10410,7 +10726,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>12.439894705167909</t>
+          <t>11.859549131951201</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -10420,7 +10736,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.33196365207995676</t>
+          <t>0.3116479326565981</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -10439,7 +10755,7 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
+          <t>structurally_resolved_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
         </is>
       </c>
     </row>
@@ -10456,12 +10772,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10476,37 +10792,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.5996758508914101</t>
+          <t>0.6412478336221837</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.8816855753646677</t>
+          <t>0.9428076256499134</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.9627228525121555</t>
+          <t>0.9722703639514731</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.4066180005201097</t>
+          <t>0.46014315364537195</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.29192339164165</t>
+          <t>1.1247880603691582</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3.63978055098988</t>
+          <t>3.079564098070489</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.8097244732576986</t>
+          <t>0.8248328794256005</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -10534,17 +10850,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.7272727272727273</t>
+          <t>0.8333333333333334</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -10554,7 +10870,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.9810363636363636</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -10564,12 +10880,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>0.9991454545454544</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.9906</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -10591,12 +10907,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10611,37 +10927,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.5996758508914101</t>
+          <t>0.6412478336221837</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.8816855753646677</t>
+          <t>0.9428076256499134</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.9627228525121555</t>
+          <t>0.9722703639514731</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.4066180005201097</t>
+          <t>0.46014315364537195</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.29192339164165</t>
+          <t>1.1247880603691582</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3.63978055098988</t>
+          <t>3.079564098070489</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.8097244732576986</t>
+          <t>0.8248328794256005</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -10669,42 +10985,42 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.5423728813559322</t>
+          <t>0.8666666666666667</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.9830508474576272</t>
+          <t>0.9666666666666667</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>0.7621084745762712</t>
+          <t>0.8712733333333333</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.6628</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>0.9388067796610169</t>
+          <t>0.98236</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.1062</t>
+          <t>0.9072</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -10840,7 +11156,7 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
+          <t>structurally_resolved_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
         </is>
       </c>
     </row>
@@ -10971,7 +11287,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
+          <t>structurally_resolved_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11688,7 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
+          <t>structurally_resolved_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
         </is>
       </c>
     </row>
@@ -11503,7 +11819,7 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
+          <t>structurally_resolved_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
         </is>
       </c>
     </row>
@@ -11904,7 +12220,7 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
+          <t>structurally_resolved_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
         </is>
       </c>
     </row>
@@ -12035,7 +12351,7 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
+          <t>structurally_resolved_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM32"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -12334,7 +12650,7 @@
     <col width="62" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="62" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
@@ -12362,6 +12678,7 @@
     <col width="62" customWidth="1" min="37" max="37"/>
     <col width="28" customWidth="1" min="38" max="38"/>
     <col width="41" customWidth="1" min="39" max="39"/>
+    <col width="62" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12670,6 +12987,11 @@
           <t>interpretation_call</t>
         </is>
       </c>
+      <c r="AN12" s="1" t="inlineStr">
+        <is>
+          <t>diagnostic_inference_scope</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12684,12 +13006,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -12704,37 +13026,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.5996758508914101</t>
+          <t>0.6412478336221837</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.8816855753646677</t>
+          <t>0.9428076256499134</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.9627228525121555</t>
+          <t>0.9722703639514731</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.4066180005201097</t>
+          <t>0.46014315364537195</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.29192339164165</t>
+          <t>1.1247880603691582</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3.63978055098988</t>
+          <t>3.079564098070489</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.8097244732576986</t>
+          <t>0.8248328794256005</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -12749,7 +13071,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.08515559157212318</t>
+          <t>0.09103708838821492</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -12759,7 +13081,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0.24147649918962724</t>
+          <t>0.2575310225303293</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -12769,7 +13091,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>14.832717215541487</t>
+          <t>13.842638296012616</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -12779,7 +13101,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.08139703943814154</t>
+          <t>0.08159509779648427</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -12798,7 +13120,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
+          <t>structurally_resolved_disrupted_genomes_only;baseline_equal_probability_null_over_observed_event_catalogue</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -12815,6 +13137,11 @@
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>heuristic_structure_reuse_diagnostic_not_formal_hypothesis_test</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12829,12 +13156,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -12849,37 +13176,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.5996758508914101</t>
+          <t>0.6412478336221837</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.8816855753646677</t>
+          <t>0.9428076256499134</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.9627228525121555</t>
+          <t>0.9722703639514731</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.4066180005201097</t>
+          <t>0.46014315364537195</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.29192339164165</t>
+          <t>1.1247880603691582</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3.63978055098988</t>
+          <t>3.079564098070489</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.8097244732576986</t>
+          <t>0.8248328794256005</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -12894,7 +13221,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.19212350081037277</t>
+          <t>0.19634350086655114</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -12904,7 +13231,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.42306126418152346</t>
+          <t>0.43198197573656855</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -12914,7 +13241,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>12.439894705167909</t>
+          <t>11.859549131951201</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -12924,7 +13251,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.33196365207995676</t>
+          <t>0.3116479326565981</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -12943,7 +13270,7 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>interpretable_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
+          <t>structurally_resolved_disrupted_genomes_only;approximate_accessibility_weights:IS481_hotspot_high,rearrangement_intermediate,other_low</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -12960,6 +13287,11 @@
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>heuristic_structure_reuse_diagnostic_not_formal_hypothesis_test</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12974,12 +13306,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -12994,37 +13326,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.5996758508914101</t>
+          <t>0.6412478336221837</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.8816855753646677</t>
+          <t>0.9428076256499134</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.9627228525121555</t>
+          <t>0.9722703639514731</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.4066180005201097</t>
+          <t>0.46014315364537195</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.29192339164165</t>
+          <t>1.1247880603691582</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3.63978055098988</t>
+          <t>3.079564098070489</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.8097244732576986</t>
+          <t>0.8248328794256005</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -13052,17 +13384,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.7272727272727273</t>
+          <t>0.8333333333333334</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -13072,7 +13404,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.9810363636363636</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -13082,17 +13414,17 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>0.9991454545454544</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.9906</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>event_labels_permuted_across_fixed_lineage_or_ST_strata;tests_independent_reuse_not_genome_burden</t>
+          <t>event_labels_permuted_across_fixed_lineage_or_ST_strata;diagnostic_screen_independent_reuse_not_genome_burden</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -13109,6 +13441,11 @@
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>heuristic_structure_reuse_diagnostic_not_formal_hypothesis_test</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13123,12 +13460,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -13143,37 +13480,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.5996758508914101</t>
+          <t>0.6412478336221837</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.8816855753646677</t>
+          <t>0.9428076256499134</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.9627228525121555</t>
+          <t>0.9722703639514731</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.4066180005201097</t>
+          <t>0.46014315364537195</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.29192339164165</t>
+          <t>1.1247880603691582</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3.63978055098988</t>
+          <t>3.079564098070489</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.8097244732576986</t>
+          <t>0.8248328794256005</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -13201,47 +13538,47 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.5423728813559322</t>
+          <t>0.8666666666666667</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.9830508474576272</t>
+          <t>0.9666666666666667</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>0.7621084745762712</t>
+          <t>0.8712733333333333</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.6628</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>0.9388067796610169</t>
+          <t>0.98236</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.1062</t>
+          <t>0.9072</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>event_labels_permuted_across_fixed_country_year_strata;tests_sampling_burst_robustness_not_genome_burden</t>
+          <t>event_labels_permuted_across_fixed_country_year_strata;diagnostic_screen_sampling_burst_robustness_not_genome_burden</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -13258,6 +13595,11 @@
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>heuristic_structure_reuse_diagnostic_not_formal_hypothesis_test</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13272,48 +13614,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1045</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap54</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.17395070977986526</t>
+          <t>0.19060431302631736</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.5218521293395958</t>
+          <t>0.5718129390789521</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.7631427352551966</t>
+          <t>0.8297069982825556</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.13540867243780158</t>
+          <t>0.1534084280948838</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.1561668231605284</t>
+          <t>2.037909131788361</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7.385051355993011</t>
+          <t>6.518546682334138</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -13334,7 +13676,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr"/>
@@ -13346,7 +13688,7 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Equal-weighted across study/BioProject blocks among interpretable disrupted genomes only.</t>
+          <t>Study-block-equalized descriptive sensitivity among structurally resolved disrupted genomes only; not a formal hypothesis test.</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -13361,12 +13703,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.8119935170178282</t>
+          <t>0.8630849220103987</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1045;prn_evt_coding_disrupted_is481__is481__gap54;prn_evt_other_disruption__insertion_like__gap204</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap54;prn_evt_coding_disrupted_is481__is481__gap1045;prn_evt_other_disruption__insertion_like__gap204</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -13377,6 +13719,11 @@
       <c r="AM17" t="inlineStr">
         <is>
           <t>concentrated_but_partly_study_amplified</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>heuristic_structure_reuse_diagnostic_not_formal_hypothesis_test</t>
         </is>
       </c>
     </row>
@@ -13393,12 +13740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -13413,32 +13760,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.4482758620689655</t>
+          <t>0.6582278481012658</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.8275862068965517</t>
+          <t>0.8354430379746836</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.9137931034482758</t>
+          <t>0.9113924050632911</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.3119797859690844</t>
+          <t>0.4532927415478289</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.5269578952962481</t>
+          <t>1.3227974278323738</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3.2053358742258222</t>
+          <t>2.206079886885825</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -13459,7 +13806,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr"/>
@@ -13471,7 +13818,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Observed event weights after removing largest block PRJNA279196.</t>
+          <t>Descriptive sensitivity after removing largest block PRJNA279196; not a formal hypothesis test.</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -13486,22 +13833,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.8119935170178282</t>
+          <t>0.8630849220103987</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1043;prn_evt_insufficient__not_available_current_step3;prn_evt_rearrangement__within_contig__cov58</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043;prn_evt_rearrangement__within_contig__cov58;prn_evt_rearrangement__within_contig__cov91</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
           <t>concentrated_but_partly_study_amplified</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>heuristic_structure_reuse_diagnostic_not_formal_hypothesis_test</t>
         </is>
       </c>
     </row>
@@ -13732,7 +14084,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -13932,18 +14284,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1045</t>
+          <t>prn_evt_coding_disrupted_is481__is481__gap54</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>is481:is481:gap1045</t>
+          <t>is481:is481:gap54</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.17395070977986526</t>
+          <t>0.19060431302631736</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -13954,7 +14306,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.5218521293395958</t>
+          <t>0.5718129390789521</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -13996,7 +14348,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.4482758620689655</t>
+          <t>0.6582278481012658</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -14007,7 +14359,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.8275862068965517</t>
+          <t>0.8354430379746836</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
